--- a/WebHost/wwwroot/import-excel/施工统计表数据导入（06、105）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工统计表数据导入（06、105）.xlsx
@@ -1,28 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41246A61-780F-403C-8F31-22A846B5DF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BABB4DC-EA07-4D40-8C1E-E4A0D9F9310D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>日期</t>
   </si>
@@ -30,95 +44,130 @@
     <t>船舶名称</t>
   </si>
   <si>
+    <t>船次</t>
+  </si>
+  <si>
+    <t>船方</t>
+  </si>
+  <si>
+    <t>检修时间</t>
+  </si>
+  <si>
+    <t>天气影响</t>
+  </si>
+  <si>
+    <t>柴油补充</t>
+  </si>
+  <si>
+    <t>柴油库存</t>
+  </si>
+  <si>
+    <t>滑油日耗</t>
+  </si>
+  <si>
+    <t>简要说明</t>
+  </si>
+  <si>
+    <t>产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停工时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水日耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水库存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑油（吨）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>作业时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>锚泊时间</t>
-  </si>
-  <si>
-    <t>检修时间</t>
-  </si>
-  <si>
-    <t>天气影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>待工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>主发电机运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停泊发电机运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴油总日耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>主发电机累计时间</t>
-  </si>
-  <si>
-    <t>停泊发电机运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>停泊发电机累计时间</t>
-  </si>
-  <si>
-    <t>日耗</t>
-  </si>
-  <si>
-    <t>补充</t>
-  </si>
-  <si>
-    <t>库存</t>
-  </si>
-  <si>
-    <t>小计</t>
-  </si>
-  <si>
-    <t>柴油补充</t>
-  </si>
-  <si>
-    <t>柴油库存</t>
-  </si>
-  <si>
-    <t>滑油日耗</t>
-  </si>
-  <si>
-    <t>简要说明</t>
-  </si>
-  <si>
-    <t>（备注：小计是柴油总日耗）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -138,17 +187,90 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -158,37 +280,58 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -208,9 +351,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -224,38 +367,38 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -283,14 +426,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -318,42 +478,85 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -367,38 +570,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -452,147 +637,149 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B800CC8-A909-447B-A086-099E135E3E25}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.125" customWidth="1"/>
-    <col min="19" max="19" width="31.875" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="7"/>
+    <col min="2" max="9" width="10.625" style="2"/>
+    <col min="10" max="13" width="12.625" style="2" customWidth="1"/>
+    <col min="14" max="16" width="10.625" style="2"/>
+    <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
+    <col min="18" max="20" width="10.625" style="2"/>
+    <col min="21" max="21" width="20.625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="10.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="13"/>
+      <c r="G1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="14"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="13"/>
+      <c r="L1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="14"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="8"/>
+    </row>
+    <row r="2" spans="1:21" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="S2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="T2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="U2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="7"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <mergeCells count="7">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" showInputMessage="1" sqref="B3:B7" xr:uid="{38A59080-3E97-44A2-A7BF-1E6239315E84}">
+      <formula1>"厦港浚001,厦港工06,厦港工105"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/WebHost/wwwroot/import-excel/施工统计表数据导入（06、105）.xlsx
+++ b/WebHost/wwwroot/import-excel/施工统计表数据导入（06、105）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\test_vs\EAM3.0\WebHost\wwwroot\import-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BABB4DC-EA07-4D40-8C1E-E4A0D9F9310D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35662B3C-B5CB-4ACF-AEA2-0C63C47BDF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06325E8B-7DA5-4057-B741-81AE4591759A}"/>
   </bookViews>
@@ -140,11 +140,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="180" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -280,7 +281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -331,6 +332,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,8 +655,9 @@
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="7"/>
-    <col min="2" max="9" width="10.625" style="2"/>
-    <col min="10" max="13" width="12.625" style="2" customWidth="1"/>
+    <col min="2" max="4" width="10.625" style="2"/>
+    <col min="5" max="9" width="10.625" style="15"/>
+    <col min="10" max="13" width="12.625" style="15" customWidth="1"/>
     <col min="14" max="16" width="10.625" style="2"/>
     <col min="17" max="17" width="12.625" style="2" customWidth="1"/>
     <col min="18" max="20" width="10.625" style="2"/>
